--- a/data/trans_orig/P23-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P23-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2007</t>
+          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>219420</t>
+          <t>217514</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>268288</t>
+          <t>266241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>459232</t>
+          <t>458586</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>505155</t>
+          <t>507479</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>687932</t>
+          <t>690526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>763913</t>
+          <t>763725</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112534</t>
+          <t>111289</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154421</t>
+          <t>153206</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31469</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57631</t>
+          <t>55408</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150630</t>
+          <t>151387</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200369</t>
+          <t>197973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27054</t>
+          <t>27396</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28190</t>
+          <t>26525</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25445</t>
+          <t>24863</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48901</t>
+          <t>48957</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>275918</t>
+          <t>275422</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>328925</t>
+          <t>331052</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122748</t>
+          <t>123393</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>164956</t>
+          <t>165275</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>410404</t>
+          <t>409907</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>479360</t>
+          <t>480048</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>336974</t>
+          <t>334289</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>399017</t>
+          <t>396515</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>631281</t>
+          <t>631524</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>688710</t>
+          <t>687650</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>984011</t>
+          <t>980486</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1071082</t>
+          <t>1070795</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,51%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>165297</t>
+          <t>164777</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>215660</t>
+          <t>214861</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63327</t>
+          <t>64657</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99058</t>
+          <t>99378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>240687</t>
+          <t>239899</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>302358</t>
+          <t>301756</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36028</t>
+          <t>37809</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25244</t>
+          <t>24412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30764</t>
+          <t>29745</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56190</t>
+          <t>56432</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>350199</t>
+          <t>350215</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>411768</t>
+          <t>414731</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>184051</t>
+          <t>186251</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>237114</t>
+          <t>237908</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>551959</t>
+          <t>551226</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>635094</t>
+          <t>635950</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>260672</t>
+          <t>264589</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>314651</t>
+          <t>317671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>449538</t>
+          <t>449044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>497822</t>
+          <t>496347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>725651</t>
+          <t>725439</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>801785</t>
+          <t>797150</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,51%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114412</t>
+          <t>113527</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>156779</t>
+          <t>155672</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28983</t>
+          <t>28658</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52570</t>
+          <t>52603</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>151137</t>
+          <t>152148</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>200180</t>
+          <t>199008</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25008</t>
+          <t>28517</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10438</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25924</t>
+          <t>26045</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>23149</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46092</t>
+          <t>45383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>213945</t>
+          <t>213669</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>263049</t>
+          <t>265915</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132132</t>
+          <t>133999</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174557</t>
+          <t>179461</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>356100</t>
+          <t>356940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425920</t>
+          <t>423604</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>335780</t>
+          <t>333395</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>392977</t>
+          <t>391278</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>604555</t>
+          <t>607726</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>670450</t>
+          <t>671081</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>957806</t>
+          <t>959590</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1044777</t>
+          <t>1046655</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,84%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>152877</t>
+          <t>151310</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197930</t>
+          <t>199492</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78126</t>
+          <t>76496</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>114732</t>
+          <t>113201</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>241765</t>
+          <t>240558</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>299039</t>
+          <t>300520</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>17474</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36719</t>
+          <t>36056</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23745</t>
+          <t>24105</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47926</t>
+          <t>48605</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42852</t>
+          <t>45899</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>74306</t>
+          <t>74714</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>352028</t>
+          <t>351866</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>413674</t>
+          <t>409815</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>244072</t>
+          <t>242255</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>299097</t>
+          <t>298976</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>606946</t>
+          <t>613026</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>691651</t>
+          <t>693717</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1200076</t>
+          <t>1203141</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1310485</t>
+          <t>1316105</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2203911</t>
+          <t>2202130</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2311143</t>
+          <t>2308664</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3434762</t>
+          <t>3439197</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3594076</t>
+          <t>3600392</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>588377</t>
+          <t>584210</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>674870</t>
+          <t>674534</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>228119</t>
+          <t>227951</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>290133</t>
+          <t>286169</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>831236</t>
+          <t>831198</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>939946</t>
+          <t>939920</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68477</t>
+          <t>70808</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>103539</t>
+          <t>106217</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>68458</t>
+          <t>68275</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>103844</t>
+          <t>102893</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>147719</t>
+          <t>145101</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>196882</t>
+          <t>197464</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1243869</t>
+          <t>1246038</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1358298</t>
+          <t>1358779</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>734097</t>
+          <t>734624</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>832959</t>
+          <t>826978</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2004640</t>
+          <t>2001220</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2158558</t>
+          <t>2163486</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2012</t>
+          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>213680</t>
+          <t>213628</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>263437</t>
+          <t>263745</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>433013</t>
+          <t>431798</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>486577</t>
+          <t>485026</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>659160</t>
+          <t>654481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>735750</t>
+          <t>740554</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>173760</t>
+          <t>170259</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>220162</t>
+          <t>220011</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57671</t>
+          <t>59090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90856</t>
+          <t>93329</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>241027</t>
+          <t>238043</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>300277</t>
+          <t>301729</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18742</t>
+          <t>17047</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23585</t>
+          <t>23054</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16028</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35081</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>233756</t>
+          <t>230620</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>285433</t>
+          <t>285499</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125913</t>
+          <t>126878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>170499</t>
+          <t>172598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>372753</t>
+          <t>372269</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>444497</t>
+          <t>442559</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>324851</t>
+          <t>325011</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>387936</t>
+          <t>387493</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>609706</t>
+          <t>608443</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>676632</t>
+          <t>677918</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>949413</t>
+          <t>947235</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1041869</t>
+          <t>1041965</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>230309</t>
+          <t>229436</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>290280</t>
+          <t>288939</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81219</t>
+          <t>80456</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120789</t>
+          <t>119407</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>320860</t>
+          <t>321964</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>390212</t>
+          <t>394008</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19401</t>
+          <t>18813</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44038</t>
+          <t>43511</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32420</t>
+          <t>33160</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36420</t>
+          <t>37641</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68886</t>
+          <t>67028</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>342834</t>
+          <t>341808</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>409690</t>
+          <t>406730</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>242254</t>
+          <t>241121</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>302225</t>
+          <t>300141</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>601007</t>
+          <t>602246</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>688372</t>
+          <t>688946</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>240013</t>
+          <t>241813</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296736</t>
+          <t>296200</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>408597</t>
+          <t>410138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>466570</t>
+          <t>468103</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>665626</t>
+          <t>665526</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>745078</t>
+          <t>747490</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,73%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>151649</t>
+          <t>151987</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>201746</t>
+          <t>200487</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87225</t>
+          <t>86873</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>128922</t>
+          <t>128933</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>252579</t>
+          <t>253036</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>315535</t>
+          <t>316456</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>19288</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40723</t>
+          <t>42222</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>13416</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34819</t>
+          <t>33099</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37132</t>
+          <t>37981</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67981</t>
+          <t>69373</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>257339</t>
+          <t>254594</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>313886</t>
+          <t>312128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184934</t>
+          <t>184239</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>238215</t>
+          <t>232878</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>451981</t>
+          <t>454174</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>532584</t>
+          <t>529615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,53%</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>346442</t>
+          <t>341128</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>406610</t>
+          <t>403830</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>609012</t>
+          <t>613638</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>676392</t>
+          <t>677390</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>972181</t>
+          <t>969039</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1061455</t>
+          <t>1059847</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180637</t>
+          <t>184014</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233667</t>
+          <t>234477</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>95064</t>
+          <t>94870</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>135848</t>
+          <t>134540</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>289611</t>
+          <t>291707</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>358396</t>
+          <t>356653</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18285</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40357</t>
+          <t>40376</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>10269</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>27191</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>33006</t>
+          <t>33574</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>59278</t>
+          <t>60251</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>307340</t>
+          <t>307311</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>370049</t>
+          <t>367944</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>249503</t>
+          <t>247414</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>307002</t>
+          <t>306338</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>572718</t>
+          <t>573496</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>656744</t>
+          <t>658850</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1169218</t>
+          <t>1174886</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1285685</t>
+          <t>1295126</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2123877</t>
+          <t>2127896</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2246418</t>
+          <t>2245641</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3322320</t>
+          <t>3339155</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3501530</t>
+          <t>3508414</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,25%</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>783459</t>
+          <t>787449</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>893771</t>
+          <t>889698</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>356331</t>
+          <t>355637</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>430372</t>
+          <t>430250</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1169229</t>
+          <t>1170752</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1298826</t>
+          <t>1299146</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76477</t>
+          <t>76667</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>119316</t>
+          <t>116998</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>57703</t>
+          <t>55338</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94330</t>
+          <t>91729</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>144947</t>
+          <t>145511</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>199703</t>
+          <t>199524</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1201751</t>
+          <t>1208657</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1322573</t>
+          <t>1318921</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>848762</t>
+          <t>846545</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>958163</t>
+          <t>954179</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2080245</t>
+          <t>2085102</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2251549</t>
+          <t>2241909</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2016</t>
+          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6886,12 +6886,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>261403</t>
+          <t>259868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>311067</t>
+          <t>310598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>411861</t>
+          <t>411846</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>461377</t>
+          <t>460358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>681234</t>
+          <t>685593</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>754261</t>
+          <t>758321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -6999,12 +6999,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118626</t>
+          <t>121279</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>161813</t>
+          <t>161871</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51404</t>
+          <t>51590</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82132</t>
+          <t>81805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>180647</t>
+          <t>179132</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>237431</t>
+          <t>232355</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7112,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>11127</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28099</t>
+          <t>28667</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>16421</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18211</t>
+          <t>18752</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39380</t>
+          <t>39478</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>209360</t>
+          <t>208943</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>256784</t>
+          <t>257851</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137847</t>
+          <t>139852</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>182210</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>359857</t>
+          <t>356314</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>430855</t>
+          <t>426460</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,67%</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>434608</t>
+          <t>434216</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>500743</t>
+          <t>500022</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>634351</t>
+          <t>630060</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>699224</t>
+          <t>694235</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1088157</t>
+          <t>1088228</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1179812</t>
+          <t>1178007</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,09%</t>
         </is>
       </c>
     </row>
@@ -7568,12 +7568,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>190433</t>
+          <t>190116</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>242472</t>
+          <t>242824</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7583,12 +7583,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87075</t>
+          <t>88115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125851</t>
+          <t>127425</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>288575</t>
+          <t>287422</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>355841</t>
+          <t>355361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -7681,12 +7681,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18063</t>
+          <t>17918</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41403</t>
+          <t>40411</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14167</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33135</t>
+          <t>34312</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36551</t>
+          <t>36678</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66292</t>
+          <t>65455</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>283958</t>
+          <t>281369</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>344156</t>
+          <t>342878</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>220199</t>
+          <t>222885</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>277245</t>
+          <t>278398</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>519852</t>
+          <t>518566</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>603779</t>
+          <t>601115</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>274017</t>
+          <t>275722</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>328828</t>
+          <t>330831</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8039,12 +8039,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>443952</t>
+          <t>445252</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>500081</t>
+          <t>501058</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>738070</t>
+          <t>735261</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>817371</t>
+          <t>818432</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,09%</t>
         </is>
       </c>
     </row>
@@ -8137,12 +8137,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>122039</t>
+          <t>124707</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>166596</t>
+          <t>168883</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63641</t>
+          <t>64857</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>100595</t>
+          <t>100184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>197628</t>
+          <t>200172</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>254949</t>
+          <t>255716</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>11205</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28549</t>
+          <t>29102</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10373</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26733</t>
+          <t>27627</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25270</t>
+          <t>25573</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48794</t>
+          <t>48872</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>266371</t>
+          <t>265594</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>322308</t>
+          <t>321670</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182421</t>
+          <t>186725</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>234493</t>
+          <t>236821</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>466440</t>
+          <t>467191</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>541892</t>
+          <t>544438</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>418886</t>
+          <t>419514</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>482112</t>
+          <t>482819</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>617540</t>
+          <t>618309</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>683434</t>
+          <t>683006</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1056760</t>
+          <t>1055867</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1144778</t>
+          <t>1149624</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>174857</t>
+          <t>174578</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>226420</t>
+          <t>226222</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>112121</t>
+          <t>111200</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>160230</t>
+          <t>158086</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>298923</t>
+          <t>300179</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>368349</t>
+          <t>369610</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>19958</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41431</t>
+          <t>41039</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15130</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36288</t>
+          <t>35604</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8889,12 +8889,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>41495</t>
+          <t>38916</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>70293</t>
+          <t>68499</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -8932,12 +8932,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>229385</t>
+          <t>233795</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>285299</t>
+          <t>289447</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>209642</t>
+          <t>207140</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>261006</t>
+          <t>262001</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>451556</t>
+          <t>453005</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>526612</t>
+          <t>532055</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1441327</t>
+          <t>1442904</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1558000</t>
+          <t>1559712</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2163871</t>
+          <t>2173783</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2283319</t>
+          <t>2285609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3646002</t>
+          <t>3647684</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3815399</t>
+          <t>3820062</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,11%</t>
         </is>
       </c>
     </row>
@@ -9275,12 +9275,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>652111</t>
+          <t>654103</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>748100</t>
+          <t>747566</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>351632</t>
+          <t>351550</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>424406</t>
+          <t>427302</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1028560</t>
+          <t>1022622</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1148926</t>
+          <t>1149943</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74832</t>
+          <t>76616</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>113688</t>
+          <t>113295</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56464</t>
+          <t>58049</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>92482</t>
+          <t>92247</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>141584</t>
+          <t>143390</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>193116</t>
+          <t>196425</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1040643</t>
+          <t>1038811</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1154044</t>
+          <t>1152918</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>801808</t>
+          <t>797859</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>902935</t>
+          <t>901243</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1867999</t>
+          <t>1866753</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2024678</t>
+          <t>2020665</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P23-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>217514</t>
+          <t>219507</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>266241</t>
+          <t>269973</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>458586</t>
+          <t>457709</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>507479</t>
+          <t>505331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>690526</t>
+          <t>689766</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>763725</t>
+          <t>764420</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,3%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>111289</t>
+          <t>111035</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>153206</t>
+          <t>152109</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>30728</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55408</t>
+          <t>56379</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151387</t>
+          <t>150530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>197973</t>
+          <t>197661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10681</t>
+          <t>10519</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27396</t>
+          <t>26968</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>11739</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26525</t>
+          <t>27720</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24863</t>
+          <t>25299</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48957</t>
+          <t>48988</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>275422</t>
+          <t>276827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>331052</t>
+          <t>327790</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>123393</t>
+          <t>124270</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>165275</t>
+          <t>164263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>409907</t>
+          <t>409049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>480048</t>
+          <t>477454</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>334289</t>
+          <t>335037</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>396515</t>
+          <t>396555</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>631524</t>
+          <t>632605</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>687650</t>
+          <t>692691</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>980486</t>
+          <t>980154</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1070795</t>
+          <t>1072426</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,59%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164777</t>
+          <t>165618</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>214861</t>
+          <t>218204</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64657</t>
+          <t>65103</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99378</t>
+          <t>99037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>239899</t>
+          <t>239570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>301756</t>
+          <t>300642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16991</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37809</t>
+          <t>37641</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8427</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24412</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29745</t>
+          <t>29656</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56432</t>
+          <t>55056</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>350215</t>
+          <t>345807</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>414731</t>
+          <t>408723</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>186251</t>
+          <t>184140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>237908</t>
+          <t>235865</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>551226</t>
+          <t>550532</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>635950</t>
+          <t>637089</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>264589</t>
+          <t>261980</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>317671</t>
+          <t>316575</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>449044</t>
+          <t>446987</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>496347</t>
+          <t>494514</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>725439</t>
+          <t>731700</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>797150</t>
+          <t>807055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>59,24%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>113527</t>
+          <t>115510</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>155672</t>
+          <t>158503</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28658</t>
+          <t>30403</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52603</t>
+          <t>53633</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>152148</t>
+          <t>150949</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>199008</t>
+          <t>200850</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28517</t>
+          <t>26271</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>25868</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23149</t>
+          <t>23087</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45383</t>
+          <t>44967</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>213669</t>
+          <t>213357</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>265915</t>
+          <t>265690</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133999</t>
+          <t>134406</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179461</t>
+          <t>177699</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>356940</t>
+          <t>357725</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>423604</t>
+          <t>424364</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>333395</t>
+          <t>330373</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>391278</t>
+          <t>390846</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>607726</t>
+          <t>607743</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>671081</t>
+          <t>672122</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>959590</t>
+          <t>955940</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1046655</t>
+          <t>1047034</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,86%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151310</t>
+          <t>152833</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>199492</t>
+          <t>200640</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76496</t>
+          <t>77916</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>113201</t>
+          <t>113678</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>240558</t>
+          <t>237019</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>300520</t>
+          <t>302721</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17474</t>
+          <t>16816</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36056</t>
+          <t>36333</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24105</t>
+          <t>24069</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48605</t>
+          <t>47600</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45899</t>
+          <t>44826</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>74714</t>
+          <t>75227</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>351866</t>
+          <t>349719</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>409815</t>
+          <t>409170</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>242255</t>
+          <t>239526</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>298976</t>
+          <t>297582</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>613026</t>
+          <t>609698</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>693717</t>
+          <t>692263</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1203141</t>
+          <t>1205655</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1316105</t>
+          <t>1315444</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2202130</t>
+          <t>2206620</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2308664</t>
+          <t>2314695</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3439197</t>
+          <t>3434129</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3600392</t>
+          <t>3602434</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>584210</t>
+          <t>582012</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>674534</t>
+          <t>674906</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>227951</t>
+          <t>226717</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>286169</t>
+          <t>289190</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>831198</t>
+          <t>837182</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>939920</t>
+          <t>943162</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>70808</t>
+          <t>67232</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>106217</t>
+          <t>103429</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>68275</t>
+          <t>68090</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>102893</t>
+          <t>102122</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>145101</t>
+          <t>143237</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>197464</t>
+          <t>196376</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1246038</t>
+          <t>1244689</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1358779</t>
+          <t>1356023</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>734624</t>
+          <t>733772</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>826978</t>
+          <t>830312</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2001220</t>
+          <t>2007914</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2163486</t>
+          <t>2158918</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>213628</t>
+          <t>210443</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>263745</t>
+          <t>263624</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>431798</t>
+          <t>436976</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>485026</t>
+          <t>489168</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>654481</t>
+          <t>660523</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>740554</t>
+          <t>738311</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,72%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>170259</t>
+          <t>173961</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>220011</t>
+          <t>222784</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59090</t>
+          <t>57401</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93329</t>
+          <t>92247</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>238043</t>
+          <t>243574</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>301729</t>
+          <t>303605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17047</t>
+          <t>17724</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23054</t>
+          <t>23258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15692</t>
+          <t>14614</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35406</t>
+          <t>34434</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>230620</t>
+          <t>234815</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>285499</t>
+          <t>286709</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>126878</t>
+          <t>128235</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>172598</t>
+          <t>173952</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>372269</t>
+          <t>372111</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>442559</t>
+          <t>443942</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>325011</t>
+          <t>320630</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>387493</t>
+          <t>383091</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>608443</t>
+          <t>610953</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>677918</t>
+          <t>677117</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>947235</t>
+          <t>945896</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1041965</t>
+          <t>1040944</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>229436</t>
+          <t>229604</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>288939</t>
+          <t>286430</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80456</t>
+          <t>78935</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119407</t>
+          <t>118969</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>321964</t>
+          <t>322736</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>394008</t>
+          <t>391424</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18813</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43511</t>
+          <t>41683</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>13652</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33160</t>
+          <t>32304</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37641</t>
+          <t>37431</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67028</t>
+          <t>67152</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>341808</t>
+          <t>347630</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>406730</t>
+          <t>409840</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>241121</t>
+          <t>240845</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>300141</t>
+          <t>300981</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>602246</t>
+          <t>603795</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>688946</t>
+          <t>690309</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241813</t>
+          <t>239697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296200</t>
+          <t>297748</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>410138</t>
+          <t>409756</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>468103</t>
+          <t>467649</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>665526</t>
+          <t>662102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>747490</t>
+          <t>744789</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,56%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>151987</t>
+          <t>152888</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>200487</t>
+          <t>202854</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>86873</t>
+          <t>88220</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>128933</t>
+          <t>127946</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>253036</t>
+          <t>255112</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>316456</t>
+          <t>320251</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19288</t>
+          <t>19606</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42222</t>
+          <t>41293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33099</t>
+          <t>33167</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37981</t>
+          <t>37962</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69373</t>
+          <t>67038</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>254594</t>
+          <t>258756</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>312128</t>
+          <t>312292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184239</t>
+          <t>182512</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>232878</t>
+          <t>233937</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>454174</t>
+          <t>459911</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>529615</t>
+          <t>535520</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>341128</t>
+          <t>339441</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>403830</t>
+          <t>406138</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>613638</t>
+          <t>610043</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>677390</t>
+          <t>673680</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>969039</t>
+          <t>975782</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1059847</t>
+          <t>1064152</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,24%</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184014</t>
+          <t>181824</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234477</t>
+          <t>235394</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>94870</t>
+          <t>94585</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>134540</t>
+          <t>135712</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>291707</t>
+          <t>289744</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>356653</t>
+          <t>359914</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17804</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40376</t>
+          <t>39368</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27191</t>
+          <t>26579</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>33574</t>
+          <t>32467</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>60251</t>
+          <t>58746</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>307311</t>
+          <t>310743</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>367944</t>
+          <t>370677</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>247414</t>
+          <t>246943</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>306338</t>
+          <t>305878</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>573496</t>
+          <t>574852</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>658850</t>
+          <t>656257</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1174886</t>
+          <t>1175351</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1295126</t>
+          <t>1290464</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2127896</t>
+          <t>2125703</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2245641</t>
+          <t>2244080</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3339155</t>
+          <t>3330702</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3508414</t>
+          <t>3507018</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,23%</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>787449</t>
+          <t>790521</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>889698</t>
+          <t>897288</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>355637</t>
+          <t>356689</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>430250</t>
+          <t>432704</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1170752</t>
+          <t>1168450</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1299146</t>
+          <t>1294079</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76667</t>
+          <t>78393</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>116998</t>
+          <t>118700</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55338</t>
+          <t>58081</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91729</t>
+          <t>94706</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>145511</t>
+          <t>145453</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>199524</t>
+          <t>200753</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1208657</t>
+          <t>1198658</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1318921</t>
+          <t>1311748</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>846545</t>
+          <t>845238</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>954179</t>
+          <t>955866</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2085102</t>
+          <t>2086356</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2241909</t>
+          <t>2242424</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -6886,12 +6886,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>259868</t>
+          <t>259987</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>310598</t>
+          <t>311716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>411846</t>
+          <t>410322</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>460358</t>
+          <t>462035</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>685593</t>
+          <t>685306</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>758321</t>
+          <t>759645</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -6999,12 +6999,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121279</t>
+          <t>119436</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>161871</t>
+          <t>161271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51590</t>
+          <t>50215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81805</t>
+          <t>81834</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179132</t>
+          <t>178625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>232355</t>
+          <t>233278</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7112,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28667</t>
+          <t>27836</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16421</t>
+          <t>17605</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18752</t>
+          <t>18735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39478</t>
+          <t>38552</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>208943</t>
+          <t>207011</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>257851</t>
+          <t>257902</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>139852</t>
+          <t>137650</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>184655</t>
+          <t>183258</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>356314</t>
+          <t>357880</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>426460</t>
+          <t>428384</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>434216</t>
+          <t>431830</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>500022</t>
+          <t>495932</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>630060</t>
+          <t>633018</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>694235</t>
+          <t>698549</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1088228</t>
+          <t>1086755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1178007</t>
+          <t>1183422</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -7568,12 +7568,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>190116</t>
+          <t>190216</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>242824</t>
+          <t>243126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7583,12 +7583,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88115</t>
+          <t>85352</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127425</t>
+          <t>124821</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>287422</t>
+          <t>288000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>355361</t>
+          <t>354706</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -7681,12 +7681,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17918</t>
+          <t>18249</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40411</t>
+          <t>42320</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34312</t>
+          <t>35133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36678</t>
+          <t>36548</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65455</t>
+          <t>65637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>281369</t>
+          <t>283684</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>342878</t>
+          <t>340721</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>222885</t>
+          <t>220756</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>278398</t>
+          <t>277963</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>518566</t>
+          <t>519097</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>601115</t>
+          <t>601620</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275722</t>
+          <t>274625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>330831</t>
+          <t>331912</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8039,12 +8039,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>445252</t>
+          <t>445753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>501058</t>
+          <t>503743</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>735261</t>
+          <t>735552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>818432</t>
+          <t>815827</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,92%</t>
         </is>
       </c>
     </row>
@@ -8137,12 +8137,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>124707</t>
+          <t>123574</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>168883</t>
+          <t>168988</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64857</t>
+          <t>64642</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>100184</t>
+          <t>102516</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>200172</t>
+          <t>200044</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>255716</t>
+          <t>257459</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11205</t>
+          <t>11620</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29102</t>
+          <t>29010</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8265,12 +8265,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27627</t>
+          <t>28596</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25573</t>
+          <t>25042</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48872</t>
+          <t>49603</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>265594</t>
+          <t>266024</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>321670</t>
+          <t>322301</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186725</t>
+          <t>184371</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>236821</t>
+          <t>234554</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>467191</t>
+          <t>465741</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>544438</t>
+          <t>542828</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>419514</t>
+          <t>420041</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>482819</t>
+          <t>481917</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>618309</t>
+          <t>618389</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>683006</t>
+          <t>682906</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1055867</t>
+          <t>1057232</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1149624</t>
+          <t>1146467</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,9%</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>174578</t>
+          <t>175044</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>226222</t>
+          <t>226118</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>111200</t>
+          <t>113304</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158086</t>
+          <t>160213</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>300179</t>
+          <t>302680</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>369610</t>
+          <t>367157</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19958</t>
+          <t>19676</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41039</t>
+          <t>41490</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>15600</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35604</t>
+          <t>35763</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8889,12 +8889,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>38916</t>
+          <t>40446</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>68499</t>
+          <t>69216</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -8932,12 +8932,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>233795</t>
+          <t>230343</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>289447</t>
+          <t>286203</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>207140</t>
+          <t>206872</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>262001</t>
+          <t>262145</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>453005</t>
+          <t>449069</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>532055</t>
+          <t>525862</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1442904</t>
+          <t>1444112</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1559712</t>
+          <t>1557913</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2173783</t>
+          <t>2164458</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2285609</t>
+          <t>2283747</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3647684</t>
+          <t>3646447</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3820062</t>
+          <t>3819124</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -9275,12 +9275,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>654103</t>
+          <t>646471</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>747566</t>
+          <t>742836</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>351550</t>
+          <t>350920</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>427302</t>
+          <t>428908</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1022622</t>
+          <t>1024460</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1149943</t>
+          <t>1147058</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76616</t>
+          <t>75516</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>113295</t>
+          <t>115618</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58049</t>
+          <t>58559</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>92247</t>
+          <t>93802</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>143390</t>
+          <t>142110</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>196425</t>
+          <t>194902</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1038811</t>
+          <t>1047905</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1152918</t>
+          <t>1151993</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>797859</t>
+          <t>800513</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>901243</t>
+          <t>906500</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1866753</t>
+          <t>1869301</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2020665</t>
+          <t>2022766</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
